--- a/excel-format/db-column-definitions_fmt-v5.0.0-ja_my-app.xlsx
+++ b/excel-format/db-column-definitions_fmt-v5.0.0-ja_my-app.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yosuke.tanaka/Desktop/development/git/ecuacion-tool-code-generator/excel-format/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46573E9E-7A3D-9E44-A74D-D4583D108F07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1139943-5B69-AD4C-BAE0-2AC34ED6D213}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="12220" tabRatio="853" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="12220" tabRatio="853" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="dataTypeプルダウン項目" sheetId="1" r:id="rId1"/>
@@ -87,9 +87,10 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata">
-  <metadataTypes count="1">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="2">
     <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
   <futureMetadata name="XLRICHVALUE" count="1">
     <bk>
@@ -100,6 +101,20 @@
       </extLst>
     </bk>
   </futureMetadata>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="2" v="0"/>
+    </bk>
+  </cellMetadata>
   <valueMetadata count="1">
     <bk>
       <rc t="1" v="0"/>
@@ -2590,277 +2605,6 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="left" vertical="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="left" vertical="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="left" vertical="center"/>
-      <border outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="6" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="6" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="left" vertical="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="center" vertical="bottom"/>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="left" vertical="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="ＭＳ Ｐゴシック"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="general" vertical="center"/>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" wrapText="1"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="general" vertical="center" wrapText="1"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="general" vertical="center" wrapText="1"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="general" vertical="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="general" vertical="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="general" vertical="center" wrapText="1"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="general" vertical="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="general" vertical="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="general" vertical="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="general" vertical="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="general" vertical="center"/>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" wrapText="1"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="right" vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.34998626667073579"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0" hidden="0"/>
     </dxf>
@@ -3334,6 +3078,277 @@
       <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="center" vertical="center"/>
     </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="left" vertical="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="left" vertical="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="left" vertical="center"/>
+      <border outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="6" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="6" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="left" vertical="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="center" vertical="bottom"/>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="left" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="general" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="general" vertical="center" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="general" vertical="center" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="general" vertical="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="general" vertical="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="general" vertical="center" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="general" vertical="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="general" vertical="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="general" vertical="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="general" vertical="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="general" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.34998626667073579"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
   <extLst>
@@ -3429,114 +3444,114 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="テーブル5" displayName="テーブル5" ref="A3:D39" totalsRowShown="0" headerRowDxfId="84" dataDxfId="83">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="テーブル5" displayName="テーブル5" ref="A3:D39" totalsRowShown="0" headerRowDxfId="114" dataDxfId="113">
   <autoFilter ref="A3:D39" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="日付" dataDxfId="82"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="バージョン" dataDxfId="81"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="修正事項" dataDxfId="80"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="修正者" dataDxfId="79"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="日付" dataDxfId="112"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="バージョン" dataDxfId="111"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="修正事項" dataDxfId="110"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="修正者" dataDxfId="109"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="テーブル50" displayName="テーブル50" ref="A5:H28" totalsRowShown="0" dataDxfId="78">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="テーブル50" displayName="テーブル50" ref="A5:H28" totalsRowShown="0" dataDxfId="123">
   <autoFilter ref="A5:H28" xr:uid="{00000000-0009-0000-0100-000004000000}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="#" dataDxfId="77">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="#" dataDxfId="122">
       <calculatedColumnFormula>ROW()-5</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0300-000008000000}" name="分類" dataDxfId="76"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="分類名" dataDxfId="75"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="項目" dataDxfId="74"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0300-000004000000}" name="説明" dataDxfId="73"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0300-000009000000}" name="必須" dataDxfId="72"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0300-000005000000}" name="値" dataDxfId="71"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0300-000006000000}" name="備考" dataDxfId="70"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0300-000008000000}" name="分類" dataDxfId="121"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="分類名" dataDxfId="120"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="項目" dataDxfId="119"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0300-000004000000}" name="説明" dataDxfId="118"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0300-000009000000}" name="必須" dataDxfId="117"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0300-000005000000}" name="値" dataDxfId="116"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0300-000006000000}" name="備考" dataDxfId="115"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="テーブル2" displayName="テーブル2" ref="A7:S37" tableType="xml" totalsRowShown="0" headerRowDxfId="69" dataDxfId="68">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="テーブル2" displayName="テーブル2" ref="A7:S37" tableType="xml" totalsRowShown="0" headerRowDxfId="108" dataDxfId="107">
   <tableColumns count="19">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" uniqueName="name" name="DataType名" dataDxfId="67">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" uniqueName="name" name="DataType名" dataDxfId="106">
       <xmlColumnPr mapId="191" xpath="/root/datatype/@name" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0400-000003000000}" uniqueName="kata" name="型" dataDxfId="66">
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0400-000003000000}" uniqueName="kata" name="型" dataDxfId="105">
       <xmlColumnPr mapId="191" xpath="/root/datatype/kata" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0400-000004000000}" uniqueName="minLength" name="長さ最小" dataDxfId="65">
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0400-000004000000}" uniqueName="minLength" name="長さ最小" dataDxfId="104">
       <xmlColumnPr mapId="191" xpath="/root/datatype/minLength" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0400-00000B000000}" uniqueName="maxLength" name="長さ最大" dataDxfId="64">
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0400-00000B000000}" uniqueName="maxLength" name="長さ最大" dataDxfId="103">
       <xmlColumnPr mapId="191" xpath="/root/datatype/maxLength" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0400-00000F000000}" uniqueName="numScale" name="データパターン（日本語）" dataDxfId="63"/>
-    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0400-000018000000}" uniqueName="stringDataPtn" name="データパターン" dataDxfId="62">
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0400-00000F000000}" uniqueName="numScale" name="データパターン（日本語）" dataDxfId="102"/>
+    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0400-000018000000}" uniqueName="stringDataPtn" name="データパターン" dataDxfId="101">
       <calculatedColumnFormula>IF(テーブル2[[#This Row],[データパターン（日本語）]]="", "", VLOOKUP(テーブル2[[#This Row],[データパターン（日本語）]],dataType・データパターン一覧!A:B,2,FALSE))</calculatedColumnFormula>
       <xmlColumnPr mapId="191" xpath="/root/datatype/stringDataPtn" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0400-000012000000}" uniqueName="18" name="禁則文字チェック除外" dataDxfId="61"/>
-    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0400-000019000000}" uniqueName="stringRegEx" name="正規表現" dataDxfId="60">
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0400-000012000000}" uniqueName="18" name="禁則文字チェック除外" dataDxfId="100"/>
+    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0400-000019000000}" uniqueName="stringRegEx" name="正規表現" dataDxfId="99">
       <xmlColumnPr mapId="191" xpath="/root/datatype/stringRegEx" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0400-000009000000}" uniqueName="numMinVal" name="最小値" dataDxfId="59">
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0400-000009000000}" uniqueName="numMinVal" name="最小値" dataDxfId="98">
       <xmlColumnPr mapId="191" xpath="/root/datatype/numMinVal" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0400-00000A000000}" uniqueName="numMaxVal" name="最大値" dataDxfId="58">
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0400-00000A000000}" uniqueName="numMaxVal" name="最大値" dataDxfId="97">
       <xmlColumnPr mapId="191" xpath="/root/datatype/numMaxVal" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0400-00000C000000}" uniqueName="numDigitInteger" name="整数部桁数" dataDxfId="57">
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0400-00000C000000}" uniqueName="numDigitInteger" name="整数部桁数" dataDxfId="96">
       <xmlColumnPr mapId="191" xpath="/root/datatype/numDigitInteger" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0400-00000D000000}" uniqueName="numDigitFraction" name="小数部桁数" dataDxfId="56">
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0400-00000D000000}" uniqueName="numDigitFraction" name="小数部桁数" dataDxfId="95">
       <xmlColumnPr mapId="191" xpath="/root/datatype/numDigitFraction" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0400-000005000000}" uniqueName="enumCodeLength" name="コードの長さ" dataDxfId="55">
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0400-000005000000}" uniqueName="enumCodeLength" name="コードの長さ" dataDxfId="94">
       <xmlColumnPr mapId="191" xpath="/root/datatype/enumCodeLength" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0400-00000E000000}" uniqueName="notNeedsTimezone" name="timezoneなし" dataDxfId="54">
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0400-00000E000000}" uniqueName="notNeedsTimezone" name="timezoneなし" dataDxfId="93">
       <xmlColumnPr mapId="191" xpath="/root/datatype/notNeedsTimezone" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0400-000010000000}" uniqueName="javadoc" name="備考" dataDxfId="53">
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0400-000010000000}" uniqueName="javadoc" name="備考" dataDxfId="92">
       <xmlColumnPr mapId="191" xpath="/root/datatype/javadoc" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" uniqueName="2" name="パターン説明（デフォルト言語）" dataDxfId="52"/>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0400-000013000000}" uniqueName="19" name="パターン説明（追加言語1）" dataDxfId="51"/>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0400-000014000000}" uniqueName="20" name="パターン説明（追加言語2）" dataDxfId="50"/>
-    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0400-000015000000}" uniqueName="21" name="パターン説明（追加言語）" dataDxfId="49"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" uniqueName="2" name="パターン説明（デフォルト言語）" dataDxfId="91"/>
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0400-000013000000}" uniqueName="19" name="パターン説明（追加言語1）" dataDxfId="90"/>
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0400-000014000000}" uniqueName="20" name="パターン説明（追加言語2）" dataDxfId="89"/>
+    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0400-000015000000}" uniqueName="21" name="パターン説明（追加言語）" dataDxfId="88"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{00000000-000C-0000-FFFF-FFFF05000000}" name="テーブル4" displayName="テーブル4" ref="A6:I33" tableType="xml" totalsRowShown="0" headerRowDxfId="48" dataDxfId="47">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{00000000-000C-0000-FFFF-FFFF05000000}" name="テーブル4" displayName="テーブル4" ref="A6:I33" tableType="xml" totalsRowShown="0" headerRowDxfId="87" dataDxfId="86">
   <autoFilter ref="A6:I33" xr:uid="{00000000-0009-0000-0100-000006000000}"/>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0500-000001000000}" uniqueName="dataTypeName" name="DataType名" dataDxfId="46">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0500-000001000000}" uniqueName="dataTypeName" name="DataType名" dataDxfId="85">
       <xmlColumnPr mapId="132" xpath="/root/enum/dataTypeName" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0500-000008000000}" uniqueName="8" name="code" dataDxfId="45"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0500-000005000000}" uniqueName="varName" name="varName" dataDxfId="44">
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0500-000008000000}" uniqueName="8" name="code" dataDxfId="84"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0500-000005000000}" uniqueName="varName" name="varName" dataDxfId="83">
       <xmlColumnPr mapId="132" xpath="/root/enum/varName" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0500-00000A000000}" uniqueName="10" name="javaのみ" dataDxfId="43"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0500-00000C000000}" uniqueName="javadoc-value" name="備考" dataDxfId="42">
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0500-00000A000000}" uniqueName="10" name="javaのみ" dataDxfId="82"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0500-00000C000000}" uniqueName="javadoc-value" name="備考" dataDxfId="81">
       <xmlColumnPr mapId="132" xpath="/root/enum/javadoc-value" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0500-000009000000}" uniqueName="9" name="表示名（デフォルト言語）" dataDxfId="41"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0500-000004000000}" uniqueName="dispNameAddLang1" name="表示名（追加言語1）" dataDxfId="40">
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0500-000009000000}" uniqueName="9" name="表示名（デフォルト言語）" dataDxfId="80"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0500-000004000000}" uniqueName="dispNameAddLang1" name="表示名（追加言語1）" dataDxfId="79">
       <xmlColumnPr mapId="132" xpath="/root/enum/dispNameAddLang1" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0500-000006000000}" uniqueName="dispNameAddLang2" name="表示名（追加言語2）" dataDxfId="39">
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0500-000006000000}" uniqueName="dispNameAddLang2" name="表示名（追加言語2）" dataDxfId="78">
       <xmlColumnPr mapId="132" xpath="/root/enum/dispNameAddLang2" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0500-000007000000}" uniqueName="dispNameAddLang3" name="表示名（追加言語3）" dataDxfId="38">
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0500-000007000000}" uniqueName="dispNameAddLang3" name="表示名（追加言語3）" dataDxfId="77">
       <xmlColumnPr mapId="132" xpath="/root/enum/dispNameAddLang3" xmlDataType="string"/>
     </tableColumn>
   </tableColumns>
@@ -3545,82 +3560,82 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{00000000-000C-0000-FFFF-FFFF06000000}" name="テーブル7" displayName="テーブル7" ref="A5:AK119" tableType="xml" totalsRowShown="0" headerRowDxfId="123" dataDxfId="122">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{00000000-000C-0000-FFFF-FFFF06000000}" name="テーブル7" displayName="テーブル7" ref="A5:AK119" tableType="xml" totalsRowShown="0" headerRowDxfId="76" dataDxfId="75">
   <autoFilter ref="A5:AK119" xr:uid="{00000000-0009-0000-0100-000007000000}"/>
   <tableColumns count="37">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0600-000001000000}" uniqueName="table" name="テーブル名" dataDxfId="121">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0600-000001000000}" uniqueName="table" name="テーブル名" dataDxfId="74">
       <xmlColumnPr mapId="161" xpath="/root/column/table" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0600-000002000000}" uniqueName="name" name="カラム名" dataDxfId="120">
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0600-000002000000}" uniqueName="name" name="カラム名" dataDxfId="73">
       <xmlColumnPr mapId="161" xpath="/root/column/@name" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0600-00000F000000}" uniqueName="dataType" name="dataType" dataDxfId="119">
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0600-00000F000000}" uniqueName="dataType" name="dataType" dataDxfId="72">
       <xmlColumnPr mapId="161" xpath="/root/column/dataType" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0600-000010000000}" uniqueName="16" name="dataType存在確認" dataDxfId="118">
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0600-000010000000}" uniqueName="16" name="dataType存在確認" dataDxfId="71">
       <calculatedColumnFormula>IF(テーブル7[[#This Row],[dataType]]="","",IF(NOT(ISNA(VLOOKUP(テーブル7[[#This Row],[dataType]], dataType定義!A:A, 1,FALSE))), "○", "×"))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="28" xr3:uid="{00000000-0010-0000-0600-00001C000000}" uniqueName="28" name="javaのみ" dataDxfId="117"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0600-000006000000}" uniqueName="pk" name="Surrogate key " dataDxfId="116">
+    <tableColumn id="28" xr3:uid="{00000000-0010-0000-0600-00001C000000}" uniqueName="28" name="javaのみ" dataDxfId="70"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0600-000006000000}" uniqueName="pk" name="Surrogate key " dataDxfId="69">
       <xmlColumnPr mapId="161" xpath="/root/column/pk" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="29" xr3:uid="{00000000-0010-0000-0600-00001D000000}" uniqueName="29" name="natural key (unique key)" dataDxfId="115"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0600-000008000000}" uniqueName="nullable" name="nullable" dataDxfId="114">
+    <tableColumn id="29" xr3:uid="{00000000-0010-0000-0600-00001D000000}" uniqueName="29" name="natural key (unique key)" dataDxfId="68"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0600-000008000000}" uniqueName="nullable" name="nullable" dataDxfId="67">
       <xmlColumnPr mapId="161" xpath="/root/column/nullable" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0600-00000A000000}" uniqueName="autoIncrement" name="自動採番" dataDxfId="113">
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0600-00000A000000}" uniqueName="autoIncrement" name="自動採番" dataDxfId="66">
       <xmlColumnPr mapId="161" xpath="/root/column/autoIncrement" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0600-000015000000}" uniqueName="forcedIncrement" name="強制採番" dataDxfId="112">
+    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0600-000015000000}" uniqueName="forcedIncrement" name="強制採番" dataDxfId="65">
       <xmlColumnPr mapId="161" xpath="/root/column/forcedIncrement" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0600-00000B000000}" uniqueName="autoUpdate" name="自動更新" dataDxfId="111">
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0600-00000B000000}" uniqueName="autoUpdate" name="自動更新" dataDxfId="64">
       <xmlColumnPr mapId="161" xpath="/root/column/autoUpdate" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0600-000014000000}" uniqueName="forcedUpdate" name="強制更新" dataDxfId="110">
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0600-000014000000}" uniqueName="forcedUpdate" name="強制更新" dataDxfId="63">
       <xmlColumnPr mapId="161" xpath="/root/column/forcedUpdate" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0600-00000C000000}" uniqueName="valueChangeMethod" name="グループ識別項目" dataDxfId="109">
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0600-00000C000000}" uniqueName="valueChangeMethod" name="グループ識別項目" dataDxfId="62">
       <xmlColumnPr mapId="161" xpath="/root/column/valueChangeMethod" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0600-000012000000}" uniqueName="updatedValue" name="SPRING監査" dataDxfId="108">
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0600-000012000000}" uniqueName="updatedValue" name="SPRING監査" dataDxfId="61">
       <xmlColumnPr mapId="161" xpath="/root/column/updatedValue" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0600-000013000000}" uniqueName="optLock" name="関連：種類" dataDxfId="107">
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0600-000013000000}" uniqueName="optLock" name="関連：種類" dataDxfId="60">
       <xmlColumnPr mapId="161" xpath="/root/column/optLock" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0600-000016000000}" uniqueName="22" name="関連：direction" dataDxfId="106"/>
-    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0600-00001A000000}" uniqueName="26" name="関連：参照元変数名" dataDxfId="105"/>
-    <tableColumn id="31" xr3:uid="{00000000-0010-0000-0600-00001F000000}" uniqueName="31" name="関連：参照元オブジェクト変数名" dataDxfId="104"/>
-    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0600-000017000000}" uniqueName="23" name="関連：参照先テーブル" dataDxfId="103"/>
-    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0600-000018000000}" uniqueName="24" name="関連：参照先カラム" dataDxfId="102"/>
-    <tableColumn id="27" xr3:uid="{00000000-0010-0000-0600-00001B000000}" uniqueName="27" name="関連：参照先変数名" dataDxfId="101"/>
-    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0600-000019000000}" uniqueName="25" name="関連：eager" dataDxfId="100"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0600-000011000000}" uniqueName="index1" name="index1" dataDxfId="99">
+    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0600-000016000000}" uniqueName="22" name="関連：direction" dataDxfId="59"/>
+    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0600-00001A000000}" uniqueName="26" name="関連：参照元変数名" dataDxfId="58"/>
+    <tableColumn id="31" xr3:uid="{00000000-0010-0000-0600-00001F000000}" uniqueName="31" name="関連：参照元オブジェクト変数名" dataDxfId="57"/>
+    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0600-000017000000}" uniqueName="23" name="関連：参照先テーブル" dataDxfId="56"/>
+    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0600-000018000000}" uniqueName="24" name="関連：参照先カラム" dataDxfId="55"/>
+    <tableColumn id="27" xr3:uid="{00000000-0010-0000-0600-00001B000000}" uniqueName="27" name="関連：参照先変数名" dataDxfId="54"/>
+    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0600-000019000000}" uniqueName="25" name="関連：eager" dataDxfId="53"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0600-000011000000}" uniqueName="index1" name="index1" dataDxfId="52">
       <xmlColumnPr mapId="161" xpath="/root/column/index1" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0600-00000E000000}" uniqueName="index2" name="index2" dataDxfId="98">
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0600-00000E000000}" uniqueName="index2" name="index2" dataDxfId="51">
       <xmlColumnPr mapId="161" xpath="/root/column/index2" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0600-00000D000000}" uniqueName="index3" name="index3" dataDxfId="97">
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0600-00000D000000}" uniqueName="index3" name="index3" dataDxfId="50">
       <xmlColumnPr mapId="161" xpath="/root/column/index3" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="34" xr3:uid="{00000000-0010-0000-0600-000022000000}" uniqueName="34" name="index4" dataDxfId="96"/>
-    <tableColumn id="35" xr3:uid="{00000000-0010-0000-0600-000023000000}" uniqueName="35" name="index5" dataDxfId="95"/>
-    <tableColumn id="36" xr3:uid="{00000000-0010-0000-0600-000024000000}" uniqueName="36" name="index6" dataDxfId="94"/>
-    <tableColumn id="37" xr3:uid="{00000000-0010-0000-0600-000025000000}" uniqueName="37" name="index7" dataDxfId="93"/>
-    <tableColumn id="38" xr3:uid="{00000000-0010-0000-0600-000026000000}" uniqueName="38" name="index8" dataDxfId="92"/>
-    <tableColumn id="39" xr3:uid="{00000000-0010-0000-0600-000027000000}" uniqueName="39" name="index9" dataDxfId="91"/>
-    <tableColumn id="40" xr3:uid="{00000000-0010-0000-0600-000028000000}" uniqueName="40" name="index10" dataDxfId="90"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0600-000005000000}" uniqueName="dispNameAddLang1" name="備考" dataDxfId="89"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0600-000009000000}" uniqueName="9" name="カラム表示名（デフォルト言語）" dataDxfId="88"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0600-000003000000}" uniqueName="dispNameAddLang1" name="カラム表示名（追加言語1）" dataDxfId="87">
+    <tableColumn id="34" xr3:uid="{00000000-0010-0000-0600-000022000000}" uniqueName="34" name="index4" dataDxfId="49"/>
+    <tableColumn id="35" xr3:uid="{00000000-0010-0000-0600-000023000000}" uniqueName="35" name="index5" dataDxfId="48"/>
+    <tableColumn id="36" xr3:uid="{00000000-0010-0000-0600-000024000000}" uniqueName="36" name="index6" dataDxfId="47"/>
+    <tableColumn id="37" xr3:uid="{00000000-0010-0000-0600-000025000000}" uniqueName="37" name="index7" dataDxfId="46"/>
+    <tableColumn id="38" xr3:uid="{00000000-0010-0000-0600-000026000000}" uniqueName="38" name="index8" dataDxfId="45"/>
+    <tableColumn id="39" xr3:uid="{00000000-0010-0000-0600-000027000000}" uniqueName="39" name="index9" dataDxfId="44"/>
+    <tableColumn id="40" xr3:uid="{00000000-0010-0000-0600-000028000000}" uniqueName="40" name="index10" dataDxfId="43"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0600-000005000000}" uniqueName="dispNameAddLang1" name="備考" dataDxfId="42"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0600-000009000000}" uniqueName="9" name="カラム表示名（デフォルト言語）" dataDxfId="41"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0600-000003000000}" uniqueName="dispNameAddLang1" name="カラム表示名（追加言語1）" dataDxfId="40">
       <xmlColumnPr mapId="161" xpath="/root/column/dispNameAddLang1" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0600-000004000000}" uniqueName="dispNameAddLang2" name="カラム表示名（追加言語2）" dataDxfId="86">
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0600-000004000000}" uniqueName="dispNameAddLang2" name="カラム表示名（追加言語2）" dataDxfId="39">
       <xmlColumnPr mapId="161" xpath="/root/column/dispNameAddLang2" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0600-000007000000}" uniqueName="dispNameAddLang3" name="カラム表示名（追加言語3）" dataDxfId="85">
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0600-000007000000}" uniqueName="dispNameAddLang3" name="カラム表示名（追加言語3）" dataDxfId="38">
       <xmlColumnPr mapId="161" xpath="/root/column/dispNameAddLang3" xmlDataType="string"/>
     </tableColumn>
   </tableColumns>
@@ -4212,8 +4227,8 @@
       </c>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="115" t="e" vm="1">
-        <f t="array" ref="A6:A22">_xlfn.UNIQUE(_xlfn._xlws.FILTER(テーブル7[テーブル名], テーブル7[テーブル名]&lt;&gt;""))</f>
+      <c r="A6" s="115" t="e" cm="1" vm="1">
+        <f t="array" ref="A6">_xlfn.UNIQUE(_xlfn._xlws.FILTER(テーブル7[テーブル名], テーブル7[テーブル名]&lt;&gt;""))</f>
         <v>#VALUE!</v>
       </c>
       <c r="B6" s="116"/>
@@ -4222,144 +4237,112 @@
       <c r="E6" s="117"/>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="118" t="e" vm="1">
-        <v>#VALUE!</v>
-      </c>
+      <c r="A7" s="118"/>
       <c r="B7" s="119"/>
       <c r="C7" s="119"/>
       <c r="D7" s="119"/>
       <c r="E7" s="120"/>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="115" t="e" vm="1">
-        <v>#VALUE!</v>
-      </c>
+      <c r="A8" s="115"/>
       <c r="B8" s="116"/>
       <c r="C8" s="116"/>
       <c r="D8" s="116"/>
       <c r="E8" s="117"/>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="118" t="e" vm="1">
-        <v>#VALUE!</v>
-      </c>
+      <c r="A9" s="118"/>
       <c r="B9" s="119"/>
       <c r="C9" s="119"/>
       <c r="D9" s="119"/>
       <c r="E9" s="120"/>
     </row>
     <row r="10" spans="1:5">
-      <c r="A10" s="115" t="e" vm="1">
-        <v>#VALUE!</v>
-      </c>
+      <c r="A10" s="115"/>
       <c r="B10" s="116"/>
       <c r="C10" s="116"/>
       <c r="D10" s="116"/>
       <c r="E10" s="117"/>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="118" t="e" vm="1">
-        <v>#VALUE!</v>
-      </c>
+      <c r="A11" s="118"/>
       <c r="B11" s="119"/>
       <c r="C11" s="119"/>
       <c r="D11" s="119"/>
       <c r="E11" s="120"/>
     </row>
     <row r="12" spans="1:5">
-      <c r="A12" s="115" t="e" vm="1">
-        <v>#VALUE!</v>
-      </c>
+      <c r="A12" s="115"/>
       <c r="B12" s="116"/>
       <c r="C12" s="116"/>
       <c r="D12" s="116"/>
       <c r="E12" s="117"/>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" s="118" t="e" vm="1">
-        <v>#VALUE!</v>
-      </c>
+      <c r="A13" s="118"/>
       <c r="B13" s="119"/>
       <c r="C13" s="119"/>
       <c r="D13" s="119"/>
       <c r="E13" s="120"/>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14" s="115" t="e" vm="1">
-        <v>#VALUE!</v>
-      </c>
+      <c r="A14" s="115"/>
       <c r="B14" s="116"/>
       <c r="C14" s="116"/>
       <c r="D14" s="116"/>
       <c r="E14" s="117"/>
     </row>
     <row r="15" spans="1:5">
-      <c r="A15" s="118" t="e" vm="1">
-        <v>#VALUE!</v>
-      </c>
+      <c r="A15" s="118"/>
       <c r="B15" s="119"/>
       <c r="C15" s="119"/>
       <c r="D15" s="119"/>
       <c r="E15" s="120"/>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" s="115" t="e" vm="1">
-        <v>#VALUE!</v>
-      </c>
+      <c r="A16" s="115"/>
       <c r="B16" s="116"/>
       <c r="C16" s="116"/>
       <c r="D16" s="116"/>
       <c r="E16" s="117"/>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="118" t="e" vm="1">
-        <v>#VALUE!</v>
-      </c>
+      <c r="A17" s="118"/>
       <c r="B17" s="119"/>
       <c r="C17" s="119"/>
       <c r="D17" s="119"/>
       <c r="E17" s="120"/>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="115" t="e" vm="1">
-        <v>#VALUE!</v>
-      </c>
+      <c r="A18" s="115"/>
       <c r="B18" s="116"/>
       <c r="C18" s="116"/>
       <c r="D18" s="116"/>
       <c r="E18" s="117"/>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="118" t="e" vm="1">
-        <v>#VALUE!</v>
-      </c>
+      <c r="A19" s="118"/>
       <c r="B19" s="119"/>
       <c r="C19" s="119"/>
       <c r="D19" s="119"/>
       <c r="E19" s="120"/>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="115" t="e" vm="1">
-        <v>#VALUE!</v>
-      </c>
+      <c r="A20" s="115"/>
       <c r="B20" s="116"/>
       <c r="C20" s="116"/>
       <c r="D20" s="116"/>
       <c r="E20" s="117"/>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="118" t="e" vm="1">
-        <v>#VALUE!</v>
-      </c>
+      <c r="A21" s="118"/>
       <c r="B21" s="119"/>
       <c r="C21" s="119"/>
       <c r="D21" s="119"/>
       <c r="E21" s="120"/>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="115" t="e" vm="1">
-        <v>#VALUE!</v>
-      </c>
+      <c r="A22" s="115"/>
       <c r="B22" s="116"/>
       <c r="C22" s="116"/>
       <c r="D22" s="116"/>

--- a/excel-format/db-column-definitions_fmt-v5.0.0-ja_my-app.xlsx
+++ b/excel-format/db-column-definitions_fmt-v5.0.0-ja_my-app.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yosuke.tanaka/Desktop/development/git/ecuacion-tool-code-generator/excel-format/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1139943-5B69-AD4C-BAE0-2AC34ED6D213}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B75BD091-4264-4D48-B147-783451EC1CA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="12220" tabRatio="853" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="12220" tabRatio="853" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="dataTypeプルダウン項目" sheetId="1" r:id="rId1"/>
@@ -124,7 +124,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="465" uniqueCount="282">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="467" uniqueCount="282">
   <si>
     <t>DB項目定義</t>
   </si>
@@ -2605,6 +2605,277 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="left" vertical="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="left" vertical="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="left" vertical="center"/>
+      <border outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="6" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="6" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="left" vertical="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="center" vertical="bottom"/>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="left" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="general" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="general" vertical="center" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="general" vertical="center" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="general" vertical="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="general" vertical="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="general" vertical="center" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="general" vertical="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="general" vertical="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="general" vertical="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="general" vertical="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="general" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.34998626667073579"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0" hidden="0"/>
     </dxf>
@@ -3078,277 +3349,6 @@
       <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="center" vertical="center"/>
     </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="left" vertical="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="left" vertical="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="left" vertical="center"/>
-      <border outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="6" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="6" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="left" vertical="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="center" vertical="bottom"/>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="left" vertical="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="ＭＳ Ｐゴシック"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="general" vertical="center"/>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" wrapText="1"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="general" vertical="center" wrapText="1"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="general" vertical="center" wrapText="1"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="general" vertical="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="general" vertical="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="general" vertical="center" wrapText="1"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="general" vertical="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="general" vertical="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="general" vertical="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="general" vertical="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="general" vertical="center"/>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" wrapText="1"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="right" vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.34998626667073579"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center"/>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
   <extLst>
@@ -3444,114 +3444,114 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="テーブル5" displayName="テーブル5" ref="A3:D39" totalsRowShown="0" headerRowDxfId="114" dataDxfId="113">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="テーブル5" displayName="テーブル5" ref="A3:D39" totalsRowShown="0" headerRowDxfId="84" dataDxfId="83">
   <autoFilter ref="A3:D39" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="日付" dataDxfId="112"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="バージョン" dataDxfId="111"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="修正事項" dataDxfId="110"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="修正者" dataDxfId="109"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="日付" dataDxfId="82"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="バージョン" dataDxfId="81"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="修正事項" dataDxfId="80"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="修正者" dataDxfId="79"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="テーブル50" displayName="テーブル50" ref="A5:H28" totalsRowShown="0" dataDxfId="123">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="テーブル50" displayName="テーブル50" ref="A5:H28" totalsRowShown="0" dataDxfId="78">
   <autoFilter ref="A5:H28" xr:uid="{00000000-0009-0000-0100-000004000000}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="#" dataDxfId="122">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="#" dataDxfId="77">
       <calculatedColumnFormula>ROW()-5</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0300-000008000000}" name="分類" dataDxfId="121"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="分類名" dataDxfId="120"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="項目" dataDxfId="119"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0300-000004000000}" name="説明" dataDxfId="118"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0300-000009000000}" name="必須" dataDxfId="117"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0300-000005000000}" name="値" dataDxfId="116"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0300-000006000000}" name="備考" dataDxfId="115"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0300-000008000000}" name="分類" dataDxfId="76"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="分類名" dataDxfId="75"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="項目" dataDxfId="74"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0300-000004000000}" name="説明" dataDxfId="73"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0300-000009000000}" name="必須" dataDxfId="72"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0300-000005000000}" name="値" dataDxfId="71"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0300-000006000000}" name="備考" dataDxfId="70"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="テーブル2" displayName="テーブル2" ref="A7:S37" tableType="xml" totalsRowShown="0" headerRowDxfId="108" dataDxfId="107">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="テーブル2" displayName="テーブル2" ref="A7:S37" tableType="xml" totalsRowShown="0" headerRowDxfId="69" dataDxfId="68">
   <tableColumns count="19">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" uniqueName="name" name="DataType名" dataDxfId="106">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" uniqueName="name" name="DataType名" dataDxfId="67">
       <xmlColumnPr mapId="191" xpath="/root/datatype/@name" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0400-000003000000}" uniqueName="kata" name="型" dataDxfId="105">
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0400-000003000000}" uniqueName="kata" name="型" dataDxfId="66">
       <xmlColumnPr mapId="191" xpath="/root/datatype/kata" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0400-000004000000}" uniqueName="minLength" name="長さ最小" dataDxfId="104">
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0400-000004000000}" uniqueName="minLength" name="長さ最小" dataDxfId="65">
       <xmlColumnPr mapId="191" xpath="/root/datatype/minLength" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0400-00000B000000}" uniqueName="maxLength" name="長さ最大" dataDxfId="103">
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0400-00000B000000}" uniqueName="maxLength" name="長さ最大" dataDxfId="64">
       <xmlColumnPr mapId="191" xpath="/root/datatype/maxLength" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0400-00000F000000}" uniqueName="numScale" name="データパターン（日本語）" dataDxfId="102"/>
-    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0400-000018000000}" uniqueName="stringDataPtn" name="データパターン" dataDxfId="101">
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0400-00000F000000}" uniqueName="numScale" name="データパターン（日本語）" dataDxfId="63"/>
+    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0400-000018000000}" uniqueName="stringDataPtn" name="データパターン" dataDxfId="62">
       <calculatedColumnFormula>IF(テーブル2[[#This Row],[データパターン（日本語）]]="", "", VLOOKUP(テーブル2[[#This Row],[データパターン（日本語）]],dataType・データパターン一覧!A:B,2,FALSE))</calculatedColumnFormula>
       <xmlColumnPr mapId="191" xpath="/root/datatype/stringDataPtn" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0400-000012000000}" uniqueName="18" name="禁則文字チェック除外" dataDxfId="100"/>
-    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0400-000019000000}" uniqueName="stringRegEx" name="正規表現" dataDxfId="99">
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0400-000012000000}" uniqueName="18" name="禁則文字チェック除外" dataDxfId="61"/>
+    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0400-000019000000}" uniqueName="stringRegEx" name="正規表現" dataDxfId="60">
       <xmlColumnPr mapId="191" xpath="/root/datatype/stringRegEx" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0400-000009000000}" uniqueName="numMinVal" name="最小値" dataDxfId="98">
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0400-000009000000}" uniqueName="numMinVal" name="最小値" dataDxfId="59">
       <xmlColumnPr mapId="191" xpath="/root/datatype/numMinVal" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0400-00000A000000}" uniqueName="numMaxVal" name="最大値" dataDxfId="97">
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0400-00000A000000}" uniqueName="numMaxVal" name="最大値" dataDxfId="58">
       <xmlColumnPr mapId="191" xpath="/root/datatype/numMaxVal" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0400-00000C000000}" uniqueName="numDigitInteger" name="整数部桁数" dataDxfId="96">
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0400-00000C000000}" uniqueName="numDigitInteger" name="整数部桁数" dataDxfId="57">
       <xmlColumnPr mapId="191" xpath="/root/datatype/numDigitInteger" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0400-00000D000000}" uniqueName="numDigitFraction" name="小数部桁数" dataDxfId="95">
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0400-00000D000000}" uniqueName="numDigitFraction" name="小数部桁数" dataDxfId="56">
       <xmlColumnPr mapId="191" xpath="/root/datatype/numDigitFraction" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0400-000005000000}" uniqueName="enumCodeLength" name="コードの長さ" dataDxfId="94">
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0400-000005000000}" uniqueName="enumCodeLength" name="コードの長さ" dataDxfId="55">
       <xmlColumnPr mapId="191" xpath="/root/datatype/enumCodeLength" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0400-00000E000000}" uniqueName="notNeedsTimezone" name="timezoneなし" dataDxfId="93">
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0400-00000E000000}" uniqueName="notNeedsTimezone" name="timezoneなし" dataDxfId="54">
       <xmlColumnPr mapId="191" xpath="/root/datatype/notNeedsTimezone" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0400-000010000000}" uniqueName="javadoc" name="備考" dataDxfId="92">
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0400-000010000000}" uniqueName="javadoc" name="備考" dataDxfId="53">
       <xmlColumnPr mapId="191" xpath="/root/datatype/javadoc" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" uniqueName="2" name="パターン説明（デフォルト言語）" dataDxfId="91"/>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0400-000013000000}" uniqueName="19" name="パターン説明（追加言語1）" dataDxfId="90"/>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0400-000014000000}" uniqueName="20" name="パターン説明（追加言語2）" dataDxfId="89"/>
-    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0400-000015000000}" uniqueName="21" name="パターン説明（追加言語）" dataDxfId="88"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" uniqueName="2" name="パターン説明（デフォルト言語）" dataDxfId="52"/>
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0400-000013000000}" uniqueName="19" name="パターン説明（追加言語1）" dataDxfId="51"/>
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0400-000014000000}" uniqueName="20" name="パターン説明（追加言語2）" dataDxfId="50"/>
+    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0400-000015000000}" uniqueName="21" name="パターン説明（追加言語）" dataDxfId="49"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{00000000-000C-0000-FFFF-FFFF05000000}" name="テーブル4" displayName="テーブル4" ref="A6:I33" tableType="xml" totalsRowShown="0" headerRowDxfId="87" dataDxfId="86">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{00000000-000C-0000-FFFF-FFFF05000000}" name="テーブル4" displayName="テーブル4" ref="A6:I33" tableType="xml" totalsRowShown="0" headerRowDxfId="48" dataDxfId="47">
   <autoFilter ref="A6:I33" xr:uid="{00000000-0009-0000-0100-000006000000}"/>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0500-000001000000}" uniqueName="dataTypeName" name="DataType名" dataDxfId="85">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0500-000001000000}" uniqueName="dataTypeName" name="DataType名" dataDxfId="46">
       <xmlColumnPr mapId="132" xpath="/root/enum/dataTypeName" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0500-000008000000}" uniqueName="8" name="code" dataDxfId="84"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0500-000005000000}" uniqueName="varName" name="varName" dataDxfId="83">
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0500-000008000000}" uniqueName="8" name="code" dataDxfId="45"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0500-000005000000}" uniqueName="varName" name="varName" dataDxfId="44">
       <xmlColumnPr mapId="132" xpath="/root/enum/varName" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0500-00000A000000}" uniqueName="10" name="javaのみ" dataDxfId="82"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0500-00000C000000}" uniqueName="javadoc-value" name="備考" dataDxfId="81">
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0500-00000A000000}" uniqueName="10" name="javaのみ" dataDxfId="43"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0500-00000C000000}" uniqueName="javadoc-value" name="備考" dataDxfId="42">
       <xmlColumnPr mapId="132" xpath="/root/enum/javadoc-value" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0500-000009000000}" uniqueName="9" name="表示名（デフォルト言語）" dataDxfId="80"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0500-000004000000}" uniqueName="dispNameAddLang1" name="表示名（追加言語1）" dataDxfId="79">
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0500-000009000000}" uniqueName="9" name="表示名（デフォルト言語）" dataDxfId="41"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0500-000004000000}" uniqueName="dispNameAddLang1" name="表示名（追加言語1）" dataDxfId="40">
       <xmlColumnPr mapId="132" xpath="/root/enum/dispNameAddLang1" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0500-000006000000}" uniqueName="dispNameAddLang2" name="表示名（追加言語2）" dataDxfId="78">
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0500-000006000000}" uniqueName="dispNameAddLang2" name="表示名（追加言語2）" dataDxfId="39">
       <xmlColumnPr mapId="132" xpath="/root/enum/dispNameAddLang2" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0500-000007000000}" uniqueName="dispNameAddLang3" name="表示名（追加言語3）" dataDxfId="77">
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0500-000007000000}" uniqueName="dispNameAddLang3" name="表示名（追加言語3）" dataDxfId="38">
       <xmlColumnPr mapId="132" xpath="/root/enum/dispNameAddLang3" xmlDataType="string"/>
     </tableColumn>
   </tableColumns>
@@ -3560,82 +3560,82 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{00000000-000C-0000-FFFF-FFFF06000000}" name="テーブル7" displayName="テーブル7" ref="A5:AK119" tableType="xml" totalsRowShown="0" headerRowDxfId="76" dataDxfId="75">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{00000000-000C-0000-FFFF-FFFF06000000}" name="テーブル7" displayName="テーブル7" ref="A5:AK119" tableType="xml" totalsRowShown="0" headerRowDxfId="123" dataDxfId="122">
   <autoFilter ref="A5:AK119" xr:uid="{00000000-0009-0000-0100-000007000000}"/>
   <tableColumns count="37">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0600-000001000000}" uniqueName="table" name="テーブル名" dataDxfId="74">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0600-000001000000}" uniqueName="table" name="テーブル名" dataDxfId="121">
       <xmlColumnPr mapId="161" xpath="/root/column/table" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0600-000002000000}" uniqueName="name" name="カラム名" dataDxfId="73">
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0600-000002000000}" uniqueName="name" name="カラム名" dataDxfId="120">
       <xmlColumnPr mapId="161" xpath="/root/column/@name" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0600-00000F000000}" uniqueName="dataType" name="dataType" dataDxfId="72">
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0600-00000F000000}" uniqueName="dataType" name="dataType" dataDxfId="119">
       <xmlColumnPr mapId="161" xpath="/root/column/dataType" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0600-000010000000}" uniqueName="16" name="dataType存在確認" dataDxfId="71">
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0600-000010000000}" uniqueName="16" name="dataType存在確認" dataDxfId="118">
       <calculatedColumnFormula>IF(テーブル7[[#This Row],[dataType]]="","",IF(NOT(ISNA(VLOOKUP(テーブル7[[#This Row],[dataType]], dataType定義!A:A, 1,FALSE))), "○", "×"))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="28" xr3:uid="{00000000-0010-0000-0600-00001C000000}" uniqueName="28" name="javaのみ" dataDxfId="70"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0600-000006000000}" uniqueName="pk" name="Surrogate key " dataDxfId="69">
+    <tableColumn id="28" xr3:uid="{00000000-0010-0000-0600-00001C000000}" uniqueName="28" name="javaのみ" dataDxfId="117"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0600-000006000000}" uniqueName="pk" name="Surrogate key " dataDxfId="116">
       <xmlColumnPr mapId="161" xpath="/root/column/pk" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="29" xr3:uid="{00000000-0010-0000-0600-00001D000000}" uniqueName="29" name="natural key (unique key)" dataDxfId="68"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0600-000008000000}" uniqueName="nullable" name="nullable" dataDxfId="67">
+    <tableColumn id="29" xr3:uid="{00000000-0010-0000-0600-00001D000000}" uniqueName="29" name="natural key (unique key)" dataDxfId="115"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0600-000008000000}" uniqueName="nullable" name="nullable" dataDxfId="114">
       <xmlColumnPr mapId="161" xpath="/root/column/nullable" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0600-00000A000000}" uniqueName="autoIncrement" name="自動採番" dataDxfId="66">
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0600-00000A000000}" uniqueName="autoIncrement" name="自動採番" dataDxfId="113">
       <xmlColumnPr mapId="161" xpath="/root/column/autoIncrement" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0600-000015000000}" uniqueName="forcedIncrement" name="強制採番" dataDxfId="65">
+    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0600-000015000000}" uniqueName="forcedIncrement" name="強制採番" dataDxfId="112">
       <xmlColumnPr mapId="161" xpath="/root/column/forcedIncrement" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0600-00000B000000}" uniqueName="autoUpdate" name="自動更新" dataDxfId="64">
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0600-00000B000000}" uniqueName="autoUpdate" name="自動更新" dataDxfId="111">
       <xmlColumnPr mapId="161" xpath="/root/column/autoUpdate" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0600-000014000000}" uniqueName="forcedUpdate" name="強制更新" dataDxfId="63">
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0600-000014000000}" uniqueName="forcedUpdate" name="強制更新" dataDxfId="110">
       <xmlColumnPr mapId="161" xpath="/root/column/forcedUpdate" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0600-00000C000000}" uniqueName="valueChangeMethod" name="グループ識別項目" dataDxfId="62">
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0600-00000C000000}" uniqueName="valueChangeMethod" name="グループ識別項目" dataDxfId="109">
       <xmlColumnPr mapId="161" xpath="/root/column/valueChangeMethod" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0600-000012000000}" uniqueName="updatedValue" name="SPRING監査" dataDxfId="61">
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0600-000012000000}" uniqueName="updatedValue" name="SPRING監査" dataDxfId="108">
       <xmlColumnPr mapId="161" xpath="/root/column/updatedValue" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0600-000013000000}" uniqueName="optLock" name="関連：種類" dataDxfId="60">
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0600-000013000000}" uniqueName="optLock" name="関連：種類" dataDxfId="107">
       <xmlColumnPr mapId="161" xpath="/root/column/optLock" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0600-000016000000}" uniqueName="22" name="関連：direction" dataDxfId="59"/>
-    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0600-00001A000000}" uniqueName="26" name="関連：参照元変数名" dataDxfId="58"/>
-    <tableColumn id="31" xr3:uid="{00000000-0010-0000-0600-00001F000000}" uniqueName="31" name="関連：参照元オブジェクト変数名" dataDxfId="57"/>
-    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0600-000017000000}" uniqueName="23" name="関連：参照先テーブル" dataDxfId="56"/>
-    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0600-000018000000}" uniqueName="24" name="関連：参照先カラム" dataDxfId="55"/>
-    <tableColumn id="27" xr3:uid="{00000000-0010-0000-0600-00001B000000}" uniqueName="27" name="関連：参照先変数名" dataDxfId="54"/>
-    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0600-000019000000}" uniqueName="25" name="関連：eager" dataDxfId="53"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0600-000011000000}" uniqueName="index1" name="index1" dataDxfId="52">
+    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0600-000016000000}" uniqueName="22" name="関連：direction" dataDxfId="106"/>
+    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0600-00001A000000}" uniqueName="26" name="関連：参照元変数名" dataDxfId="105"/>
+    <tableColumn id="31" xr3:uid="{00000000-0010-0000-0600-00001F000000}" uniqueName="31" name="関連：参照元オブジェクト変数名" dataDxfId="104"/>
+    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0600-000017000000}" uniqueName="23" name="関連：参照先テーブル" dataDxfId="103"/>
+    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0600-000018000000}" uniqueName="24" name="関連：参照先カラム" dataDxfId="102"/>
+    <tableColumn id="27" xr3:uid="{00000000-0010-0000-0600-00001B000000}" uniqueName="27" name="関連：参照先変数名" dataDxfId="101"/>
+    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0600-000019000000}" uniqueName="25" name="関連：eager" dataDxfId="100"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0600-000011000000}" uniqueName="index1" name="index1" dataDxfId="99">
       <xmlColumnPr mapId="161" xpath="/root/column/index1" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0600-00000E000000}" uniqueName="index2" name="index2" dataDxfId="51">
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0600-00000E000000}" uniqueName="index2" name="index2" dataDxfId="98">
       <xmlColumnPr mapId="161" xpath="/root/column/index2" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0600-00000D000000}" uniqueName="index3" name="index3" dataDxfId="50">
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0600-00000D000000}" uniqueName="index3" name="index3" dataDxfId="97">
       <xmlColumnPr mapId="161" xpath="/root/column/index3" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="34" xr3:uid="{00000000-0010-0000-0600-000022000000}" uniqueName="34" name="index4" dataDxfId="49"/>
-    <tableColumn id="35" xr3:uid="{00000000-0010-0000-0600-000023000000}" uniqueName="35" name="index5" dataDxfId="48"/>
-    <tableColumn id="36" xr3:uid="{00000000-0010-0000-0600-000024000000}" uniqueName="36" name="index6" dataDxfId="47"/>
-    <tableColumn id="37" xr3:uid="{00000000-0010-0000-0600-000025000000}" uniqueName="37" name="index7" dataDxfId="46"/>
-    <tableColumn id="38" xr3:uid="{00000000-0010-0000-0600-000026000000}" uniqueName="38" name="index8" dataDxfId="45"/>
-    <tableColumn id="39" xr3:uid="{00000000-0010-0000-0600-000027000000}" uniqueName="39" name="index9" dataDxfId="44"/>
-    <tableColumn id="40" xr3:uid="{00000000-0010-0000-0600-000028000000}" uniqueName="40" name="index10" dataDxfId="43"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0600-000005000000}" uniqueName="dispNameAddLang1" name="備考" dataDxfId="42"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0600-000009000000}" uniqueName="9" name="カラム表示名（デフォルト言語）" dataDxfId="41"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0600-000003000000}" uniqueName="dispNameAddLang1" name="カラム表示名（追加言語1）" dataDxfId="40">
+    <tableColumn id="34" xr3:uid="{00000000-0010-0000-0600-000022000000}" uniqueName="34" name="index4" dataDxfId="96"/>
+    <tableColumn id="35" xr3:uid="{00000000-0010-0000-0600-000023000000}" uniqueName="35" name="index5" dataDxfId="95"/>
+    <tableColumn id="36" xr3:uid="{00000000-0010-0000-0600-000024000000}" uniqueName="36" name="index6" dataDxfId="94"/>
+    <tableColumn id="37" xr3:uid="{00000000-0010-0000-0600-000025000000}" uniqueName="37" name="index7" dataDxfId="93"/>
+    <tableColumn id="38" xr3:uid="{00000000-0010-0000-0600-000026000000}" uniqueName="38" name="index8" dataDxfId="92"/>
+    <tableColumn id="39" xr3:uid="{00000000-0010-0000-0600-000027000000}" uniqueName="39" name="index9" dataDxfId="91"/>
+    <tableColumn id="40" xr3:uid="{00000000-0010-0000-0600-000028000000}" uniqueName="40" name="index10" dataDxfId="90"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0600-000005000000}" uniqueName="dispNameAddLang1" name="備考" dataDxfId="89"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0600-000009000000}" uniqueName="9" name="カラム表示名（デフォルト言語）" dataDxfId="88"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0600-000003000000}" uniqueName="dispNameAddLang1" name="カラム表示名（追加言語1）" dataDxfId="87">
       <xmlColumnPr mapId="161" xpath="/root/column/dispNameAddLang1" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0600-000004000000}" uniqueName="dispNameAddLang2" name="カラム表示名（追加言語2）" dataDxfId="39">
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0600-000004000000}" uniqueName="dispNameAddLang2" name="カラム表示名（追加言語2）" dataDxfId="86">
       <xmlColumnPr mapId="161" xpath="/root/column/dispNameAddLang2" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0600-000007000000}" uniqueName="dispNameAddLang3" name="カラム表示名（追加言語3）" dataDxfId="38">
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0600-000007000000}" uniqueName="dispNameAddLang3" name="カラム表示名（追加言語3）" dataDxfId="85">
       <xmlColumnPr mapId="161" xpath="/root/column/dispNameAddLang3" xmlDataType="string"/>
     </tableColumn>
   </tableColumns>
@@ -5688,7 +5688,9 @@
       <c r="E27" s="15" t="s">
         <v>244</v>
       </c>
-      <c r="F27" s="27"/>
+      <c r="F27" s="27" t="s">
+        <v>199</v>
+      </c>
       <c r="G27" s="1"/>
       <c r="H27" s="1"/>
     </row>
@@ -5709,7 +5711,9 @@
       <c r="E28" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="F28" s="4"/>
+      <c r="F28" s="27" t="s">
+        <v>199</v>
+      </c>
       <c r="G28" s="1"/>
       <c r="H28" s="1"/>
     </row>

--- a/excel-format/db-column-definitions_fmt-v5.0.0-ja_my-app.xlsx
+++ b/excel-format/db-column-definitions_fmt-v5.0.0-ja_my-app.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yosuke.tanaka/Desktop/development/git/ecuacion-tool-code-generator/excel-format/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B75BD091-4264-4D48-B147-783451EC1CA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69FFBBC5-97D7-7A43-8E70-ED886AF0A2BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="12220" tabRatio="853" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -124,7 +124,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="467" uniqueCount="282">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="282">
   <si>
     <t>DB項目定義</t>
   </si>
@@ -2605,277 +2605,6 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="left" vertical="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="left" vertical="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="left" vertical="center"/>
-      <border outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="6" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="6" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="left" vertical="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="center" vertical="bottom"/>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="left" vertical="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="ＭＳ Ｐゴシック"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="general" vertical="center"/>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" wrapText="1"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="general" vertical="center" wrapText="1"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="general" vertical="center" wrapText="1"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="general" vertical="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="general" vertical="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="general" vertical="center" wrapText="1"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="general" vertical="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="general" vertical="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="general" vertical="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="general" vertical="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="general" vertical="center"/>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" wrapText="1"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="right" vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.34998626667073579"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0" hidden="0"/>
     </dxf>
@@ -3349,6 +3078,277 @@
       <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="center" vertical="center"/>
     </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="left" vertical="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="left" vertical="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="left" vertical="center"/>
+      <border outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="6" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="6" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="left" vertical="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="center" vertical="bottom"/>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="left" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="general" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="general" vertical="center" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="general" vertical="center" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="general" vertical="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="general" vertical="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="general" vertical="center" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="general" vertical="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="general" vertical="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="general" vertical="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="general" vertical="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="general" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.34998626667073579"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
   <extLst>
@@ -3444,114 +3444,114 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="テーブル5" displayName="テーブル5" ref="A3:D39" totalsRowShown="0" headerRowDxfId="84" dataDxfId="83">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="テーブル5" displayName="テーブル5" ref="A3:D39" totalsRowShown="0" headerRowDxfId="114" dataDxfId="113">
   <autoFilter ref="A3:D39" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="日付" dataDxfId="82"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="バージョン" dataDxfId="81"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="修正事項" dataDxfId="80"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="修正者" dataDxfId="79"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="日付" dataDxfId="112"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="バージョン" dataDxfId="111"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="修正事項" dataDxfId="110"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="修正者" dataDxfId="109"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="テーブル50" displayName="テーブル50" ref="A5:H28" totalsRowShown="0" dataDxfId="78">
-  <autoFilter ref="A5:H28" xr:uid="{00000000-0009-0000-0100-000004000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="テーブル50" displayName="テーブル50" ref="A5:H27" totalsRowShown="0" dataDxfId="123">
+  <autoFilter ref="A5:H27" xr:uid="{00000000-0009-0000-0100-000004000000}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="#" dataDxfId="77">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="#" dataDxfId="122">
       <calculatedColumnFormula>ROW()-5</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0300-000008000000}" name="分類" dataDxfId="76"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="分類名" dataDxfId="75"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="項目" dataDxfId="74"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0300-000004000000}" name="説明" dataDxfId="73"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0300-000009000000}" name="必須" dataDxfId="72"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0300-000005000000}" name="値" dataDxfId="71"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0300-000006000000}" name="備考" dataDxfId="70"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0300-000008000000}" name="分類" dataDxfId="121"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="分類名" dataDxfId="120"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="項目" dataDxfId="119"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0300-000004000000}" name="説明" dataDxfId="118"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0300-000009000000}" name="必須" dataDxfId="117"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0300-000005000000}" name="値" dataDxfId="116"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0300-000006000000}" name="備考" dataDxfId="115"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="テーブル2" displayName="テーブル2" ref="A7:S37" tableType="xml" totalsRowShown="0" headerRowDxfId="69" dataDxfId="68">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="テーブル2" displayName="テーブル2" ref="A7:S37" tableType="xml" totalsRowShown="0" headerRowDxfId="108" dataDxfId="107">
   <tableColumns count="19">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" uniqueName="name" name="DataType名" dataDxfId="67">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" uniqueName="name" name="DataType名" dataDxfId="106">
       <xmlColumnPr mapId="191" xpath="/root/datatype/@name" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0400-000003000000}" uniqueName="kata" name="型" dataDxfId="66">
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0400-000003000000}" uniqueName="kata" name="型" dataDxfId="105">
       <xmlColumnPr mapId="191" xpath="/root/datatype/kata" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0400-000004000000}" uniqueName="minLength" name="長さ最小" dataDxfId="65">
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0400-000004000000}" uniqueName="minLength" name="長さ最小" dataDxfId="104">
       <xmlColumnPr mapId="191" xpath="/root/datatype/minLength" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0400-00000B000000}" uniqueName="maxLength" name="長さ最大" dataDxfId="64">
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0400-00000B000000}" uniqueName="maxLength" name="長さ最大" dataDxfId="103">
       <xmlColumnPr mapId="191" xpath="/root/datatype/maxLength" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0400-00000F000000}" uniqueName="numScale" name="データパターン（日本語）" dataDxfId="63"/>
-    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0400-000018000000}" uniqueName="stringDataPtn" name="データパターン" dataDxfId="62">
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0400-00000F000000}" uniqueName="numScale" name="データパターン（日本語）" dataDxfId="102"/>
+    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0400-000018000000}" uniqueName="stringDataPtn" name="データパターン" dataDxfId="101">
       <calculatedColumnFormula>IF(テーブル2[[#This Row],[データパターン（日本語）]]="", "", VLOOKUP(テーブル2[[#This Row],[データパターン（日本語）]],dataType・データパターン一覧!A:B,2,FALSE))</calculatedColumnFormula>
       <xmlColumnPr mapId="191" xpath="/root/datatype/stringDataPtn" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0400-000012000000}" uniqueName="18" name="禁則文字チェック除外" dataDxfId="61"/>
-    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0400-000019000000}" uniqueName="stringRegEx" name="正規表現" dataDxfId="60">
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0400-000012000000}" uniqueName="18" name="禁則文字チェック除外" dataDxfId="100"/>
+    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0400-000019000000}" uniqueName="stringRegEx" name="正規表現" dataDxfId="99">
       <xmlColumnPr mapId="191" xpath="/root/datatype/stringRegEx" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0400-000009000000}" uniqueName="numMinVal" name="最小値" dataDxfId="59">
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0400-000009000000}" uniqueName="numMinVal" name="最小値" dataDxfId="98">
       <xmlColumnPr mapId="191" xpath="/root/datatype/numMinVal" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0400-00000A000000}" uniqueName="numMaxVal" name="最大値" dataDxfId="58">
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0400-00000A000000}" uniqueName="numMaxVal" name="最大値" dataDxfId="97">
       <xmlColumnPr mapId="191" xpath="/root/datatype/numMaxVal" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0400-00000C000000}" uniqueName="numDigitInteger" name="整数部桁数" dataDxfId="57">
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0400-00000C000000}" uniqueName="numDigitInteger" name="整数部桁数" dataDxfId="96">
       <xmlColumnPr mapId="191" xpath="/root/datatype/numDigitInteger" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0400-00000D000000}" uniqueName="numDigitFraction" name="小数部桁数" dataDxfId="56">
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0400-00000D000000}" uniqueName="numDigitFraction" name="小数部桁数" dataDxfId="95">
       <xmlColumnPr mapId="191" xpath="/root/datatype/numDigitFraction" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0400-000005000000}" uniqueName="enumCodeLength" name="コードの長さ" dataDxfId="55">
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0400-000005000000}" uniqueName="enumCodeLength" name="コードの長さ" dataDxfId="94">
       <xmlColumnPr mapId="191" xpath="/root/datatype/enumCodeLength" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0400-00000E000000}" uniqueName="notNeedsTimezone" name="timezoneなし" dataDxfId="54">
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0400-00000E000000}" uniqueName="notNeedsTimezone" name="timezoneなし" dataDxfId="93">
       <xmlColumnPr mapId="191" xpath="/root/datatype/notNeedsTimezone" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0400-000010000000}" uniqueName="javadoc" name="備考" dataDxfId="53">
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0400-000010000000}" uniqueName="javadoc" name="備考" dataDxfId="92">
       <xmlColumnPr mapId="191" xpath="/root/datatype/javadoc" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" uniqueName="2" name="パターン説明（デフォルト言語）" dataDxfId="52"/>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0400-000013000000}" uniqueName="19" name="パターン説明（追加言語1）" dataDxfId="51"/>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0400-000014000000}" uniqueName="20" name="パターン説明（追加言語2）" dataDxfId="50"/>
-    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0400-000015000000}" uniqueName="21" name="パターン説明（追加言語）" dataDxfId="49"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" uniqueName="2" name="パターン説明（デフォルト言語）" dataDxfId="91"/>
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0400-000013000000}" uniqueName="19" name="パターン説明（追加言語1）" dataDxfId="90"/>
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0400-000014000000}" uniqueName="20" name="パターン説明（追加言語2）" dataDxfId="89"/>
+    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0400-000015000000}" uniqueName="21" name="パターン説明（追加言語）" dataDxfId="88"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{00000000-000C-0000-FFFF-FFFF05000000}" name="テーブル4" displayName="テーブル4" ref="A6:I33" tableType="xml" totalsRowShown="0" headerRowDxfId="48" dataDxfId="47">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{00000000-000C-0000-FFFF-FFFF05000000}" name="テーブル4" displayName="テーブル4" ref="A6:I33" tableType="xml" totalsRowShown="0" headerRowDxfId="87" dataDxfId="86">
   <autoFilter ref="A6:I33" xr:uid="{00000000-0009-0000-0100-000006000000}"/>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0500-000001000000}" uniqueName="dataTypeName" name="DataType名" dataDxfId="46">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0500-000001000000}" uniqueName="dataTypeName" name="DataType名" dataDxfId="85">
       <xmlColumnPr mapId="132" xpath="/root/enum/dataTypeName" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0500-000008000000}" uniqueName="8" name="code" dataDxfId="45"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0500-000005000000}" uniqueName="varName" name="varName" dataDxfId="44">
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0500-000008000000}" uniqueName="8" name="code" dataDxfId="84"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0500-000005000000}" uniqueName="varName" name="varName" dataDxfId="83">
       <xmlColumnPr mapId="132" xpath="/root/enum/varName" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0500-00000A000000}" uniqueName="10" name="javaのみ" dataDxfId="43"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0500-00000C000000}" uniqueName="javadoc-value" name="備考" dataDxfId="42">
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0500-00000A000000}" uniqueName="10" name="javaのみ" dataDxfId="82"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0500-00000C000000}" uniqueName="javadoc-value" name="備考" dataDxfId="81">
       <xmlColumnPr mapId="132" xpath="/root/enum/javadoc-value" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0500-000009000000}" uniqueName="9" name="表示名（デフォルト言語）" dataDxfId="41"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0500-000004000000}" uniqueName="dispNameAddLang1" name="表示名（追加言語1）" dataDxfId="40">
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0500-000009000000}" uniqueName="9" name="表示名（デフォルト言語）" dataDxfId="80"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0500-000004000000}" uniqueName="dispNameAddLang1" name="表示名（追加言語1）" dataDxfId="79">
       <xmlColumnPr mapId="132" xpath="/root/enum/dispNameAddLang1" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0500-000006000000}" uniqueName="dispNameAddLang2" name="表示名（追加言語2）" dataDxfId="39">
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0500-000006000000}" uniqueName="dispNameAddLang2" name="表示名（追加言語2）" dataDxfId="78">
       <xmlColumnPr mapId="132" xpath="/root/enum/dispNameAddLang2" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0500-000007000000}" uniqueName="dispNameAddLang3" name="表示名（追加言語3）" dataDxfId="38">
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0500-000007000000}" uniqueName="dispNameAddLang3" name="表示名（追加言語3）" dataDxfId="77">
       <xmlColumnPr mapId="132" xpath="/root/enum/dispNameAddLang3" xmlDataType="string"/>
     </tableColumn>
   </tableColumns>
@@ -3560,82 +3560,82 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{00000000-000C-0000-FFFF-FFFF06000000}" name="テーブル7" displayName="テーブル7" ref="A5:AK119" tableType="xml" totalsRowShown="0" headerRowDxfId="123" dataDxfId="122">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{00000000-000C-0000-FFFF-FFFF06000000}" name="テーブル7" displayName="テーブル7" ref="A5:AK119" tableType="xml" totalsRowShown="0" headerRowDxfId="76" dataDxfId="75">
   <autoFilter ref="A5:AK119" xr:uid="{00000000-0009-0000-0100-000007000000}"/>
   <tableColumns count="37">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0600-000001000000}" uniqueName="table" name="テーブル名" dataDxfId="121">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0600-000001000000}" uniqueName="table" name="テーブル名" dataDxfId="74">
       <xmlColumnPr mapId="161" xpath="/root/column/table" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0600-000002000000}" uniqueName="name" name="カラム名" dataDxfId="120">
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0600-000002000000}" uniqueName="name" name="カラム名" dataDxfId="73">
       <xmlColumnPr mapId="161" xpath="/root/column/@name" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0600-00000F000000}" uniqueName="dataType" name="dataType" dataDxfId="119">
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0600-00000F000000}" uniqueName="dataType" name="dataType" dataDxfId="72">
       <xmlColumnPr mapId="161" xpath="/root/column/dataType" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0600-000010000000}" uniqueName="16" name="dataType存在確認" dataDxfId="118">
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0600-000010000000}" uniqueName="16" name="dataType存在確認" dataDxfId="71">
       <calculatedColumnFormula>IF(テーブル7[[#This Row],[dataType]]="","",IF(NOT(ISNA(VLOOKUP(テーブル7[[#This Row],[dataType]], dataType定義!A:A, 1,FALSE))), "○", "×"))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="28" xr3:uid="{00000000-0010-0000-0600-00001C000000}" uniqueName="28" name="javaのみ" dataDxfId="117"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0600-000006000000}" uniqueName="pk" name="Surrogate key " dataDxfId="116">
+    <tableColumn id="28" xr3:uid="{00000000-0010-0000-0600-00001C000000}" uniqueName="28" name="javaのみ" dataDxfId="70"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0600-000006000000}" uniqueName="pk" name="Surrogate key " dataDxfId="69">
       <xmlColumnPr mapId="161" xpath="/root/column/pk" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="29" xr3:uid="{00000000-0010-0000-0600-00001D000000}" uniqueName="29" name="natural key (unique key)" dataDxfId="115"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0600-000008000000}" uniqueName="nullable" name="nullable" dataDxfId="114">
+    <tableColumn id="29" xr3:uid="{00000000-0010-0000-0600-00001D000000}" uniqueName="29" name="natural key (unique key)" dataDxfId="68"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0600-000008000000}" uniqueName="nullable" name="nullable" dataDxfId="67">
       <xmlColumnPr mapId="161" xpath="/root/column/nullable" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0600-00000A000000}" uniqueName="autoIncrement" name="自動採番" dataDxfId="113">
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0600-00000A000000}" uniqueName="autoIncrement" name="自動採番" dataDxfId="66">
       <xmlColumnPr mapId="161" xpath="/root/column/autoIncrement" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0600-000015000000}" uniqueName="forcedIncrement" name="強制採番" dataDxfId="112">
+    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0600-000015000000}" uniqueName="forcedIncrement" name="強制採番" dataDxfId="65">
       <xmlColumnPr mapId="161" xpath="/root/column/forcedIncrement" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0600-00000B000000}" uniqueName="autoUpdate" name="自動更新" dataDxfId="111">
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0600-00000B000000}" uniqueName="autoUpdate" name="自動更新" dataDxfId="64">
       <xmlColumnPr mapId="161" xpath="/root/column/autoUpdate" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0600-000014000000}" uniqueName="forcedUpdate" name="強制更新" dataDxfId="110">
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0600-000014000000}" uniqueName="forcedUpdate" name="強制更新" dataDxfId="63">
       <xmlColumnPr mapId="161" xpath="/root/column/forcedUpdate" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0600-00000C000000}" uniqueName="valueChangeMethod" name="グループ識別項目" dataDxfId="109">
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0600-00000C000000}" uniqueName="valueChangeMethod" name="グループ識別項目" dataDxfId="62">
       <xmlColumnPr mapId="161" xpath="/root/column/valueChangeMethod" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0600-000012000000}" uniqueName="updatedValue" name="SPRING監査" dataDxfId="108">
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0600-000012000000}" uniqueName="updatedValue" name="SPRING監査" dataDxfId="61">
       <xmlColumnPr mapId="161" xpath="/root/column/updatedValue" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0600-000013000000}" uniqueName="optLock" name="関連：種類" dataDxfId="107">
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0600-000013000000}" uniqueName="optLock" name="関連：種類" dataDxfId="60">
       <xmlColumnPr mapId="161" xpath="/root/column/optLock" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0600-000016000000}" uniqueName="22" name="関連：direction" dataDxfId="106"/>
-    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0600-00001A000000}" uniqueName="26" name="関連：参照元変数名" dataDxfId="105"/>
-    <tableColumn id="31" xr3:uid="{00000000-0010-0000-0600-00001F000000}" uniqueName="31" name="関連：参照元オブジェクト変数名" dataDxfId="104"/>
-    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0600-000017000000}" uniqueName="23" name="関連：参照先テーブル" dataDxfId="103"/>
-    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0600-000018000000}" uniqueName="24" name="関連：参照先カラム" dataDxfId="102"/>
-    <tableColumn id="27" xr3:uid="{00000000-0010-0000-0600-00001B000000}" uniqueName="27" name="関連：参照先変数名" dataDxfId="101"/>
-    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0600-000019000000}" uniqueName="25" name="関連：eager" dataDxfId="100"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0600-000011000000}" uniqueName="index1" name="index1" dataDxfId="99">
+    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0600-000016000000}" uniqueName="22" name="関連：direction" dataDxfId="59"/>
+    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0600-00001A000000}" uniqueName="26" name="関連：参照元変数名" dataDxfId="58"/>
+    <tableColumn id="31" xr3:uid="{00000000-0010-0000-0600-00001F000000}" uniqueName="31" name="関連：参照元オブジェクト変数名" dataDxfId="57"/>
+    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0600-000017000000}" uniqueName="23" name="関連：参照先テーブル" dataDxfId="56"/>
+    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0600-000018000000}" uniqueName="24" name="関連：参照先カラム" dataDxfId="55"/>
+    <tableColumn id="27" xr3:uid="{00000000-0010-0000-0600-00001B000000}" uniqueName="27" name="関連：参照先変数名" dataDxfId="54"/>
+    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0600-000019000000}" uniqueName="25" name="関連：eager" dataDxfId="53"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0600-000011000000}" uniqueName="index1" name="index1" dataDxfId="52">
       <xmlColumnPr mapId="161" xpath="/root/column/index1" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0600-00000E000000}" uniqueName="index2" name="index2" dataDxfId="98">
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0600-00000E000000}" uniqueName="index2" name="index2" dataDxfId="51">
       <xmlColumnPr mapId="161" xpath="/root/column/index2" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0600-00000D000000}" uniqueName="index3" name="index3" dataDxfId="97">
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0600-00000D000000}" uniqueName="index3" name="index3" dataDxfId="50">
       <xmlColumnPr mapId="161" xpath="/root/column/index3" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="34" xr3:uid="{00000000-0010-0000-0600-000022000000}" uniqueName="34" name="index4" dataDxfId="96"/>
-    <tableColumn id="35" xr3:uid="{00000000-0010-0000-0600-000023000000}" uniqueName="35" name="index5" dataDxfId="95"/>
-    <tableColumn id="36" xr3:uid="{00000000-0010-0000-0600-000024000000}" uniqueName="36" name="index6" dataDxfId="94"/>
-    <tableColumn id="37" xr3:uid="{00000000-0010-0000-0600-000025000000}" uniqueName="37" name="index7" dataDxfId="93"/>
-    <tableColumn id="38" xr3:uid="{00000000-0010-0000-0600-000026000000}" uniqueName="38" name="index8" dataDxfId="92"/>
-    <tableColumn id="39" xr3:uid="{00000000-0010-0000-0600-000027000000}" uniqueName="39" name="index9" dataDxfId="91"/>
-    <tableColumn id="40" xr3:uid="{00000000-0010-0000-0600-000028000000}" uniqueName="40" name="index10" dataDxfId="90"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0600-000005000000}" uniqueName="dispNameAddLang1" name="備考" dataDxfId="89"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0600-000009000000}" uniqueName="9" name="カラム表示名（デフォルト言語）" dataDxfId="88"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0600-000003000000}" uniqueName="dispNameAddLang1" name="カラム表示名（追加言語1）" dataDxfId="87">
+    <tableColumn id="34" xr3:uid="{00000000-0010-0000-0600-000022000000}" uniqueName="34" name="index4" dataDxfId="49"/>
+    <tableColumn id="35" xr3:uid="{00000000-0010-0000-0600-000023000000}" uniqueName="35" name="index5" dataDxfId="48"/>
+    <tableColumn id="36" xr3:uid="{00000000-0010-0000-0600-000024000000}" uniqueName="36" name="index6" dataDxfId="47"/>
+    <tableColumn id="37" xr3:uid="{00000000-0010-0000-0600-000025000000}" uniqueName="37" name="index7" dataDxfId="46"/>
+    <tableColumn id="38" xr3:uid="{00000000-0010-0000-0600-000026000000}" uniqueName="38" name="index8" dataDxfId="45"/>
+    <tableColumn id="39" xr3:uid="{00000000-0010-0000-0600-000027000000}" uniqueName="39" name="index9" dataDxfId="44"/>
+    <tableColumn id="40" xr3:uid="{00000000-0010-0000-0600-000028000000}" uniqueName="40" name="index10" dataDxfId="43"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0600-000005000000}" uniqueName="dispNameAddLang1" name="備考" dataDxfId="42"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0600-000009000000}" uniqueName="9" name="カラム表示名（デフォルト言語）" dataDxfId="41"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0600-000003000000}" uniqueName="dispNameAddLang1" name="カラム表示名（追加言語1）" dataDxfId="40">
       <xmlColumnPr mapId="161" xpath="/root/column/dispNameAddLang1" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0600-000004000000}" uniqueName="dispNameAddLang2" name="カラム表示名（追加言語2）" dataDxfId="86">
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0600-000004000000}" uniqueName="dispNameAddLang2" name="カラム表示名（追加言語2）" dataDxfId="39">
       <xmlColumnPr mapId="161" xpath="/root/column/dispNameAddLang2" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0600-000007000000}" uniqueName="dispNameAddLang3" name="カラム表示名（追加言語3）" dataDxfId="85">
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0600-000007000000}" uniqueName="dispNameAddLang3" name="カラム表示名（追加言語3）" dataDxfId="38">
       <xmlColumnPr mapId="161" xpath="/root/column/dispNameAddLang3" xmlDataType="string"/>
     </tableColumn>
   </tableColumns>
@@ -5167,7 +5167,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:H28"/>
+  <dimension ref="A1:H27"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="4.5" bestFit="1" customWidth="1"/>
@@ -5218,7 +5218,7 @@
     </row>
     <row r="6" spans="1:8" ht="16" customHeight="1">
       <c r="A6" s="1">
-        <f t="shared" ref="A6:A28" si="0">ROW()-5</f>
+        <f t="shared" ref="A6:A27" si="0">ROW()-5</f>
         <v>1</v>
       </c>
       <c r="B6" s="1" t="s">
@@ -5693,29 +5693,6 @@
       </c>
       <c r="G27" s="1"/>
       <c r="H27" s="1"/>
-    </row>
-    <row r="28" spans="1:8" ht="16" customHeight="1">
-      <c r="A28" s="1">
-        <f t="shared" si="0"/>
-        <v>23</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>242</v>
-      </c>
-      <c r="C28" s="15" t="s">
-        <v>243</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="F28" s="27" t="s">
-        <v>199</v>
-      </c>
-      <c r="G28" s="1"/>
-      <c r="H28" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/excel-format/db-column-definitions_fmt-v5.0.0-ja_my-app.xlsx
+++ b/excel-format/db-column-definitions_fmt-v5.0.0-ja_my-app.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10802"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yosuke.tanaka/Desktop/development/git/ecuacion-tool-code-generator/excel-format/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69FFBBC5-97D7-7A43-8E70-ED886AF0A2BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{554C91CB-6C7B-1F46-871F-FC33190DB484}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="12220" tabRatio="853" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="6860" windowWidth="28800" windowHeight="10300" tabRatio="853" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="dataTypeプルダウン項目" sheetId="1" r:id="rId1"/>
@@ -124,7 +124,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="282">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="466" uniqueCount="285">
   <si>
     <t>DB項目定義</t>
   </si>
@@ -1145,6 +1145,15 @@
   </si>
   <si>
     <t>テーブル表示名（追加言語3）</t>
+  </si>
+  <si>
+    <t>VERSION</t>
+  </si>
+  <si>
+    <t>UTF-8</t>
+  </si>
+  <si>
+    <t>ja</t>
   </si>
 </sst>
 </file>
@@ -4194,7 +4203,7 @@
     <row r="3" spans="1:5">
       <c r="B3" s="32" t="str">
         <f>IF(各種設定!$G$11=0,"",各種設定!$G$11)</f>
-        <v/>
+        <v>ja</v>
       </c>
       <c r="C3" s="32" t="str">
         <f>IF(各種設定!$G$12=0,"",各種設定!$G$12)</f>
@@ -5307,7 +5316,9 @@
       <c r="F9" s="27" t="s">
         <v>199</v>
       </c>
-      <c r="G9" s="1"/>
+      <c r="G9" s="1" t="s">
+        <v>48</v>
+      </c>
       <c r="H9" s="1"/>
     </row>
     <row r="10" spans="1:8" ht="16" customHeight="1">
@@ -5330,7 +5341,9 @@
       <c r="F10" s="27" t="s">
         <v>199</v>
       </c>
-      <c r="G10" s="1"/>
+      <c r="G10" s="1" t="s">
+        <v>283</v>
+      </c>
       <c r="H10" s="1"/>
     </row>
     <row r="11" spans="1:8" ht="32" customHeight="1">
@@ -5353,7 +5366,9 @@
       <c r="F11" s="27" t="s">
         <v>199</v>
       </c>
-      <c r="G11" s="1"/>
+      <c r="G11" s="1" t="s">
+        <v>284</v>
+      </c>
       <c r="H11" s="1"/>
     </row>
     <row r="12" spans="1:8" ht="48" customHeight="1">
@@ -5691,7 +5706,9 @@
       <c r="F27" s="27" t="s">
         <v>199</v>
       </c>
-      <c r="G27" s="1"/>
+      <c r="G27" s="1" t="s">
+        <v>282</v>
+      </c>
       <c r="H27" s="1"/>
     </row>
   </sheetData>
@@ -5699,18 +5716,6 @@
   <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{B1E060DA-7E17-4942-B37C-4D18258907E1}">
-          <x14:formula1>
-            <xm:f>dataTypeプルダウン項目!$C$3:$C$5</xm:f>
-          </x14:formula1>
-          <xm:sqref>G9</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-  </extLst>
 </worksheet>
 </file>
 
@@ -5763,7 +5768,7 @@
       <c r="B3" s="3"/>
       <c r="P3" s="32" t="str">
         <f>IF(各種設定!$G$11=0,"",各種設定!$G$11)</f>
-        <v/>
+        <v>ja</v>
       </c>
       <c r="Q3" s="32" t="str">
         <f>IF(各種設定!$G$12=0,"",各種設定!$G$12)</f>
@@ -6734,7 +6739,7 @@
       <c r="D4" s="52"/>
       <c r="F4" s="32" t="str">
         <f>IF(各種設定!$G$11=0,"",各種設定!$G$11)</f>
-        <v/>
+        <v>ja</v>
       </c>
       <c r="G4" s="32" t="str">
         <f>IF(各種設定!$G$12=0,"",各種設定!$G$12)</f>
@@ -7137,7 +7142,7 @@
       <c r="A3" s="52"/>
       <c r="AH3" s="32" t="str">
         <f>IF(各種設定!$G$11=0,"",各種設定!$G$11)</f>
-        <v/>
+        <v>ja</v>
       </c>
       <c r="AI3" s="32" t="str">
         <f>IF(各種設定!$G$12=0,"",各種設定!$G$12)</f>
@@ -12150,7 +12155,7 @@
       <c r="A3" s="52"/>
       <c r="AH3" s="32" t="str">
         <f>IF(各種設定!$G$11=0,"",各種設定!$G$11)</f>
-        <v/>
+        <v>ja</v>
       </c>
       <c r="AI3" s="32" t="str">
         <f>IF(各種設定!$G$12=0,"",各種設定!$G$12)</f>

--- a/excel-format/db-column-definitions_fmt-v5.0.0-ja_my-app.xlsx
+++ b/excel-format/db-column-definitions_fmt-v5.0.0-ja_my-app.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yosuke.tanaka/Desktop/development/git/ecuacion-tool-code-generator/excel-format/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{554C91CB-6C7B-1F46-871F-FC33190DB484}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34E6D80B-00B6-3248-8FD2-39F50E0E6587}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="6860" windowWidth="28800" windowHeight="10300" tabRatio="853" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="2320" windowWidth="28800" windowHeight="14820" tabRatio="853" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="dataTypeプルダウン項目" sheetId="1" r:id="rId1"/>
+    <sheet name="dataTypeプルダウン項目" sheetId="1" state="hidden" r:id="rId1"/>
     <sheet name="dataType・データパターン一覧" sheetId="2" state="hidden" r:id="rId2"/>
     <sheet name="FK種類" sheetId="3" state="hidden" r:id="rId3"/>
     <sheet name="fmt変更履歴" sheetId="4" r:id="rId4"/>

--- a/excel-format/db-column-definitions_fmt-v5.0.0-ja_my-app.xlsx
+++ b/excel-format/db-column-definitions_fmt-v5.0.0-ja_my-app.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yosuke.tanaka/Desktop/development/git/ecuacion-tool-code-generator/excel-format/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34E6D80B-00B6-3248-8FD2-39F50E0E6587}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DDF771A-570F-834B-890D-90434FB761DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="2320" windowWidth="28800" windowHeight="14820" tabRatio="853" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="2320" windowWidth="28800" windowHeight="14820" tabRatio="853" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="dataTypeプルダウン項目" sheetId="1" state="hidden" r:id="rId1"/>
@@ -124,7 +124,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="466" uniqueCount="285">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="471" uniqueCount="285">
   <si>
     <t>DB項目定義</t>
   </si>
@@ -3466,8 +3466,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="テーブル50" displayName="テーブル50" ref="A5:H27" totalsRowShown="0" dataDxfId="123">
-  <autoFilter ref="A5:H27" xr:uid="{00000000-0009-0000-0100-000004000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="テーブル50" displayName="テーブル50" ref="A5:H28" totalsRowShown="0" dataDxfId="123">
+  <autoFilter ref="A5:H28" xr:uid="{00000000-0009-0000-0100-000004000000}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="#" dataDxfId="122">
       <calculatedColumnFormula>ROW()-5</calculatedColumnFormula>
@@ -5176,7 +5176,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:H27"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="4.5" bestFit="1" customWidth="1"/>
@@ -5710,6 +5710,29 @@
         <v>282</v>
       </c>
       <c r="H27" s="1"/>
+    </row>
+    <row r="28" spans="1:8" ht="16">
+      <c r="A28" s="1">
+        <f>ROW()-5</f>
+        <v>23</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="C28" s="15" t="s">
+        <v>243</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="F28" s="27" t="s">
+        <v>199</v>
+      </c>
+      <c r="G28" s="1"/>
+      <c r="H28" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
